--- a/data/attendance/ECOLE_عمير_علمي.xlsx
+++ b/data/attendance/ECOLE_عمير_علمي.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
@@ -23,13 +20,6 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:a00b5e0f-4b92-4a58-ad0a-f851b10286b7</t>
         </r>
       </text>
@@ -37,13 +27,6 @@
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:dd35d9fe-24d8-4041-8674-1d6b7c2d016b</t>
         </r>
       </text>
@@ -51,13 +34,6 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:b8ef0e08-e53b-4bb6-8a66-50674cdd08e8</t>
         </r>
       </text>
@@ -65,13 +41,6 @@
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:35a8850e-384f-4968-9da3-c3eb22525bb1</t>
         </r>
       </text>
@@ -79,13 +48,6 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:48ca8012-4a6b-4eb8-b9b7-a646aefb32b5</t>
         </r>
       </text>
@@ -93,13 +55,6 @@
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:c50583ed-f80f-4807-8d3d-2fd0796b6dec</t>
         </r>
       </text>
@@ -107,13 +62,6 @@
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:71d0abec-2b1b-49d2-870d-c036d9b372d5</t>
         </r>
       </text>
@@ -121,13 +69,6 @@
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:c48161d3-629c-442b-acdb-fb08c3cd50d9</t>
         </r>
       </text>
@@ -135,13 +76,6 @@
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:33c29f7f-9445-49e9-b866-f9037067f20f</t>
         </r>
       </text>
@@ -149,13 +83,6 @@
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:4f5e518f-86be-48da-a41a-9fbd818e3f99</t>
         </r>
       </text>
@@ -163,13 +90,6 @@
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:ab0c805d-75fe-4651-836b-337ff2ee87a3</t>
         </r>
       </text>
@@ -177,13 +97,6 @@
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6005aae3-a206-4e48-8f54-d198748b652f</t>
         </r>
       </text>
@@ -191,13 +104,6 @@
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:572ee111-f2e7-441c-9878-32ded822147a</t>
         </r>
       </text>
@@ -205,13 +111,6 @@
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:a4f94c43-a8d5-4655-9c82-21649e29f7b1</t>
         </r>
       </text>
@@ -219,13 +118,6 @@
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:40855229-a2ef-4a2d-bd91-30978be26039</t>
         </r>
       </text>
@@ -233,13 +125,6 @@
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:8987d150-6a68-44fb-b39d-68aaddd05382</t>
         </r>
       </text>
@@ -249,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>عمير علمي  |  ECOLE  |  BAC  |  عمير اسماء</t>
   </si>
@@ -263,6 +148,9 @@
     <t>has_books=true</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -284,7 +172,14 @@
     <t>30/09/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">كتاب
+    <t>03/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كتاب 1
+ت 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كتاب 2
 ت 1</t>
   </si>
   <si>
@@ -371,7 +266,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -393,40 +291,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="666666"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="12">
@@ -529,7 +420,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -890,15 +781,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R20"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -918,8 +809,9 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
-    </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -929,10 +821,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -972,83 +867,89 @@
         <v>0</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>5</v>
-      </c>
       <c r="H4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>31</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="10">
         <v>0</v>
@@ -1078,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="11">
         <v>0</v>
@@ -1086,19 +987,22 @@
       <c r="Q5" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R5" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>55</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="12">
         <v>0</v>
@@ -1139,22 +1043,25 @@
       <c r="Q6" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R6" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>68</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="10">
         <v>0</v>
@@ -1192,22 +1099,25 @@
       <c r="Q7" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R7" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>112</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" s="12">
         <v>0</v>
       </c>
       <c r="D8" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="12">
         <v>0</v>
@@ -1237,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" s="11">
         <v>0</v>
@@ -1245,22 +1155,25 @@
       <c r="Q8" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R8" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>120</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" s="10">
         <v>0</v>
       </c>
       <c r="D9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="10">
         <v>0</v>
@@ -1290,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" s="11">
         <v>0</v>
@@ -1298,22 +1211,25 @@
       <c r="Q9" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R9" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>694</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C10" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="12">
         <v>0</v>
@@ -1343,7 +1259,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="11">
         <v>0</v>
@@ -1351,13 +1267,16 @@
       <c r="Q10" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>695</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C11" s="10">
         <v>0</v>
@@ -1404,22 +1323,25 @@
       <c r="Q11" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R11" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>696</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C12" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="12">
         <v>0</v>
@@ -1449,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="11">
         <v>0</v>
@@ -1457,22 +1379,25 @@
       <c r="Q12" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R12" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>697</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="10">
         <v>0</v>
@@ -1510,22 +1435,25 @@
       <c r="Q13" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R13" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>698</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C14" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="12">
         <v>0</v>
@@ -1563,22 +1491,25 @@
       <c r="Q14" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R14" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>699</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C15" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="10">
         <v>0</v>
@@ -1608,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="11">
         <v>0</v>
@@ -1616,22 +1547,25 @@
       <c r="Q15" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R15" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>700</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C16" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="12">
         <v>0</v>
@@ -1661,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="11">
         <v>0</v>
@@ -1669,19 +1603,22 @@
       <c r="Q16" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>701</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C17" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="10">
         <v>0</v>
@@ -1722,22 +1659,25 @@
       <c r="Q17" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>702</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C18" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="12">
         <v>0</v>
@@ -1775,13 +1715,16 @@
       <c r="Q18" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>820</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C19" s="10">
         <v>0</v>
@@ -1790,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="10">
         <v>0</v>
@@ -1820,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" s="11">
         <v>0</v>
@@ -1828,13 +1771,16 @@
       <c r="Q19" s="11">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" ht="18.95" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>825</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C20" s="12">
         <v>0</v>
@@ -1843,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="12">
         <v>0</v>
@@ -1873,22 +1819,25 @@
         <v>0</v>
       </c>
       <c r="O20" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="11">
         <v>0</v>
       </c>
       <c r="Q20" s="11">
+        <v>0</v>
+      </c>
+      <c r="R20" s="11">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:R1"/>
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1898,89 +1847,94 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>